--- a/FinanceDataMigration/src/main/resources/migration-templates/BANK_ACCOUNT.xlsx
+++ b/FinanceDataMigration/src/main/resources/migration-templates/BANK_ACCOUNT.xlsx
@@ -215,19 +215,17 @@
     <font>
       <b/>
       <sz val="11.000000"/>
-      <color indexed="64"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color indexed="2"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <color indexed="64"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -237,7 +235,7 @@
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -288,22 +286,22 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -12917,41 +12915,12 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <dataValidations count="6" disablePrompts="0">
-    <dataValidation sqref="C4:C1000" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'Bank Branch'!$D$4:$D$44</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G1000" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$L$2:$L$1000</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F1000" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>Fund!$C$4:$C$1000</formula1>
-    </dataValidation>
-    <dataValidation sqref="B4:B1000" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$1000</formula1>
-    </dataValidation>
-    <dataValidation sqref="J4:J1000" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$M$2:$M$1000</formula1>
-    </dataValidation>
-    <dataValidation sqref="D4:D1000" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'Bank Branch'!$E$4:$E$44</formula1>
-    </dataValidation>
+  <dataValidations count="1" disablePrompts="0">
+    <dataValidation sqref="1:1048576" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
   </dataValidations>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
   <headerFooter/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{5F93F426-2109-416F-8EA4-CF0A0D4ABFB5}" type="custom" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="1" showErrorMessage="1" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>COUNTIF($E$4:$E$1000,E4)=1</xm:f>
-          </x14:formula1>
-          <xm:sqref>E4:E1000</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>